--- a/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
+++ b/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Time to Fixation Experiments - Changing Chemotaxis Equation\Experiment 3 - SOS vs Random Mutation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A051AE5-1EE5-4612-80B8-61750A3FD3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6EB7C8-933D-4BEA-B8B1-8B5EC67FC70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
   <sheets>
     <sheet name="All Time Distributions" sheetId="2" r:id="rId1"/>
@@ -2054,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B6A8E3-D8EB-4280-840A-346B01586132}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -2072,6 +2072,56 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>32277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>59194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>46634</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>73295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>26560</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>24715</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>56414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>72929</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>25697</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>86400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
+++ b/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Time to Fixation Experiments - Changing Chemotaxis Equation\Experiment 3 - SOS vs Random Mutation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6EB7C8-933D-4BEA-B8B1-8B5EC67FC70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E41E630-A6EF-429B-97ED-AEDE1CB5A4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
   <sheets>
     <sheet name="All Time Distributions" sheetId="2" r:id="rId1"/>
@@ -424,502 +424,802 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>16634</v>
+        <v>17623</v>
+      </c>
+      <c r="B2">
+        <v>32277</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>22472</v>
+        <v>21652</v>
+      </c>
+      <c r="B3">
+        <v>59194</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>15586</v>
+        <v>20515</v>
+      </c>
+      <c r="B4">
+        <v>46634</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>15735</v>
+        <v>19787</v>
+      </c>
+      <c r="B5">
+        <v>73295</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>15363</v>
+        <v>19868</v>
+      </c>
+      <c r="B6">
+        <v>26560</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>16444</v>
+        <v>19822</v>
+      </c>
+      <c r="B7">
+        <v>24715</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>16198</v>
+        <v>16763</v>
+      </c>
+      <c r="B8">
+        <v>56414</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>17846</v>
+        <v>17699</v>
+      </c>
+      <c r="B9">
+        <v>72929</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>15841</v>
+        <v>19191</v>
+      </c>
+      <c r="B10">
+        <v>25697</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>17363</v>
+        <v>27387</v>
+      </c>
+      <c r="B11">
+        <v>86400</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>14760</v>
+        <v>19778</v>
+      </c>
+      <c r="B12">
+        <v>82886</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>18310</v>
+        <v>22791</v>
+      </c>
+      <c r="B13">
+        <v>49086</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>14800</v>
+        <v>17237</v>
+      </c>
+      <c r="B14">
+        <v>32180</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>15814</v>
+        <v>29302</v>
+      </c>
+      <c r="B15">
+        <v>62021</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>18416</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18526</v>
+      </c>
+      <c r="B16">
+        <v>20933</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16894</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19676</v>
+      </c>
+      <c r="B17">
+        <v>43428</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>23383</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17917</v>
+      </c>
+      <c r="B18">
+        <v>68500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>16284</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22714</v>
+      </c>
+      <c r="B19">
+        <v>18811</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>20268</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19125</v>
+      </c>
+      <c r="B20">
+        <v>21682</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>18299</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18403</v>
+      </c>
+      <c r="B21">
+        <v>21703</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>15518</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19929</v>
+      </c>
+      <c r="B22">
+        <v>30874</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>18258</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19198</v>
+      </c>
+      <c r="B23">
+        <v>56130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>14661</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21127</v>
+      </c>
+      <c r="B24">
+        <v>40566</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>18435</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21274</v>
+      </c>
+      <c r="B25">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>15699</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18723</v>
+      </c>
+      <c r="B26">
+        <v>31588</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>17490</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21532</v>
+      </c>
+      <c r="B27">
+        <v>73878</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>17610</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19670</v>
+      </c>
+      <c r="B28">
+        <v>30991</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>19275</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21113</v>
+      </c>
+      <c r="B29">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>15778</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19465</v>
+      </c>
+      <c r="B30">
+        <v>52802</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>16835</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+        <v>16728</v>
+      </c>
+      <c r="B31">
+        <v>56560</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>17221</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21089</v>
+      </c>
+      <c r="B32">
+        <v>25229</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>15998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+        <v>23554</v>
+      </c>
+      <c r="B33">
+        <v>47442</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>15551</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19923</v>
+      </c>
+      <c r="B34">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>16320</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18413</v>
+      </c>
+      <c r="B35">
+        <v>32426</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>17597</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20004</v>
+      </c>
+      <c r="B36">
+        <v>34126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>16577</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21440</v>
+      </c>
+      <c r="B37">
+        <v>71863</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>17523</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20410</v>
+      </c>
+      <c r="B38">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>16864</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18257</v>
+      </c>
+      <c r="B39">
+        <v>80639</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>17102</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18387</v>
+      </c>
+      <c r="B40">
+        <v>23770</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>17282</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17769</v>
+      </c>
+      <c r="B41">
+        <v>36796</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>16472</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18215</v>
+      </c>
+      <c r="B42">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>14526</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18278</v>
+      </c>
+      <c r="B43">
+        <v>42456</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>16708</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+        <v>15891</v>
+      </c>
+      <c r="B44">
+        <v>46865</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>17392</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18170</v>
+      </c>
+      <c r="B45">
+        <v>39012</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>18781</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+        <v>16296</v>
+      </c>
+      <c r="B46">
+        <v>57032</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>17353</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18997</v>
+      </c>
+      <c r="B47">
+        <v>27628</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>19775</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18869</v>
+      </c>
+      <c r="B48">
+        <v>24297</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>16158</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22535</v>
+      </c>
+      <c r="B49">
+        <v>60003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>15542</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21755</v>
+      </c>
+      <c r="B50">
+        <v>46577</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>19375</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21313</v>
+      </c>
+      <c r="B51">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>16775</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17382</v>
+      </c>
+      <c r="B52">
+        <v>25892</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>14966</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+        <v>14158</v>
+      </c>
+      <c r="B53">
+        <v>31129</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>18290</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20453</v>
+      </c>
+      <c r="B54">
+        <v>20795</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>16439</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22570</v>
+      </c>
+      <c r="B55">
+        <v>52130</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>16085</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19834</v>
+      </c>
+      <c r="B56">
+        <v>30922</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>15109</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18073</v>
+      </c>
+      <c r="B57">
+        <v>19406</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>16827</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18467</v>
+      </c>
+      <c r="B58">
+        <v>50145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>17459</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21549</v>
+      </c>
+      <c r="B59">
+        <v>32009</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>16333</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18859</v>
+      </c>
+      <c r="B60">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>16709</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20866</v>
+      </c>
+      <c r="B61">
+        <v>16011</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>17258</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+        <v>15488</v>
+      </c>
+      <c r="B62">
+        <v>38381</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>14761</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18316</v>
+      </c>
+      <c r="B63">
+        <v>19573</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>16775</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+        <v>16757</v>
+      </c>
+      <c r="B64">
+        <v>60334</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>14020</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19529</v>
+      </c>
+      <c r="B65">
+        <v>21026</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>16239</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17115</v>
+      </c>
+      <c r="B66">
+        <v>63215</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>14369</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19810</v>
+      </c>
+      <c r="B67">
+        <v>61757</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>17432</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19675</v>
+      </c>
+      <c r="B68">
+        <v>31685</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>17718</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18232</v>
+      </c>
+      <c r="B69">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>15054</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22855</v>
+      </c>
+      <c r="B70">
+        <v>53183</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>14690</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19714</v>
+      </c>
+      <c r="B71">
+        <v>22151</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>18087</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18637</v>
+      </c>
+      <c r="B72">
+        <v>52395</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>15455</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21934</v>
+      </c>
+      <c r="B73">
+        <v>37095</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>17360</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17978</v>
+      </c>
+      <c r="B74">
+        <v>74801</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>20873</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18861</v>
+      </c>
+      <c r="B75">
+        <v>37757</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>17800</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21769</v>
+      </c>
+      <c r="B76">
+        <v>50038</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>17082</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20414</v>
+      </c>
+      <c r="B77">
+        <v>23750</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>17010</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+        <v>15837</v>
+      </c>
+      <c r="B78">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>16223</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21813</v>
+      </c>
+      <c r="B79">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>20619</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17380</v>
+      </c>
+      <c r="B80">
+        <v>36391</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>17068</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20122</v>
+      </c>
+      <c r="B81">
+        <v>64251</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>18559</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19410</v>
+      </c>
+      <c r="B82">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>16719</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22338</v>
+      </c>
+      <c r="B83">
+        <v>53476</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>18323</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18991</v>
+      </c>
+      <c r="B84">
+        <v>25874</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>16893</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17290</v>
+      </c>
+      <c r="B85">
+        <v>78489</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>19397</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20010</v>
+      </c>
+      <c r="B86">
+        <v>73979</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>17573</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21678</v>
+      </c>
+      <c r="B87">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>16644</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19946</v>
+      </c>
+      <c r="B88">
+        <v>57069</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>16510</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17375</v>
+      </c>
+      <c r="B89">
+        <v>29866</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>17834</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20391</v>
+      </c>
+      <c r="B90">
+        <v>42467</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>16340</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+        <v>23005</v>
+      </c>
+      <c r="B91">
+        <v>82097</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>17189</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17818</v>
+      </c>
+      <c r="B92">
+        <v>27486</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>15984</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18917</v>
+      </c>
+      <c r="B93">
+        <v>53809</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>17181</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19667</v>
+      </c>
+      <c r="B94">
+        <v>78106</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>17910</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18383</v>
+      </c>
+      <c r="B95">
+        <v>20883</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>18310</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19588</v>
+      </c>
+      <c r="B96">
+        <v>26449</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>15632</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18280</v>
+      </c>
+      <c r="B97">
+        <v>17196</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>17093</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25153</v>
+      </c>
+      <c r="B98">
+        <v>46726</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>23264</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20100</v>
+      </c>
+      <c r="B99">
+        <v>43138</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>15585</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+        <v>16033</v>
+      </c>
+      <c r="B100">
+        <v>26322</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>12418</v>
+        <v>19924</v>
+      </c>
+      <c r="B101">
+        <v>27136</v>
       </c>
     </row>
   </sheetData>
@@ -949,1102 +1249,1102 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>16634</v>
+        <v>17623</v>
       </c>
       <c r="B2">
-        <v>277.23333333333335</v>
+        <v>293.71666666666664</v>
       </c>
       <c r="C2">
-        <v>4.6205555555555557</v>
+        <v>4.8952777777777774</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>22472</v>
+        <v>21652</v>
       </c>
       <c r="B3">
-        <v>374.53333333333336</v>
+        <v>360.86666666666667</v>
       </c>
       <c r="C3">
-        <v>6.2422222222222219</v>
+        <v>6.014444444444444</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>15586</v>
+        <v>20515</v>
       </c>
       <c r="B4">
-        <v>259.76666666666665</v>
+        <v>341.91666666666669</v>
       </c>
       <c r="C4">
-        <v>4.3294444444444444</v>
+        <v>5.6986111111111111</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>15735</v>
+        <v>19787</v>
       </c>
       <c r="B5">
-        <v>262.25</v>
+        <v>329.78333333333336</v>
       </c>
       <c r="C5">
-        <v>4.3708333333333336</v>
+        <v>5.4963888888888892</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>15363</v>
+        <v>19868</v>
       </c>
       <c r="B6">
-        <v>256.05</v>
+        <v>331.13333333333333</v>
       </c>
       <c r="C6">
-        <v>4.2675000000000001</v>
+        <v>5.5188888888888892</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>16444</v>
+        <v>19822</v>
       </c>
       <c r="B7">
-        <v>274.06666666666666</v>
+        <v>330.36666666666667</v>
       </c>
       <c r="C7">
-        <v>4.5677777777777777</v>
+        <v>5.5061111111111112</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>16198</v>
+        <v>16763</v>
       </c>
       <c r="B8">
-        <v>269.96666666666664</v>
+        <v>279.38333333333333</v>
       </c>
       <c r="C8">
-        <v>4.4994444444444444</v>
+        <v>4.6563888888888885</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>17846</v>
+        <v>17699</v>
       </c>
       <c r="B9">
-        <v>297.43333333333334</v>
+        <v>294.98333333333335</v>
       </c>
       <c r="C9">
-        <v>4.9572222222222226</v>
+        <v>4.9163888888888891</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>15841</v>
+        <v>19191</v>
       </c>
       <c r="B10">
-        <v>264.01666666666665</v>
+        <v>319.85000000000002</v>
       </c>
       <c r="C10">
-        <v>4.4002777777777782</v>
+        <v>5.3308333333333335</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>17363</v>
+        <v>27387</v>
       </c>
       <c r="B11">
-        <v>289.38333333333333</v>
+        <v>456.45</v>
       </c>
       <c r="C11">
-        <v>4.8230555555555554</v>
+        <v>7.6074999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>14760</v>
+        <v>19778</v>
       </c>
       <c r="B12">
-        <v>246</v>
+        <v>329.63333333333333</v>
       </c>
       <c r="C12">
-        <v>4.0999999999999996</v>
+        <v>5.4938888888888888</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>18310</v>
+        <v>22791</v>
       </c>
       <c r="B13">
-        <v>305.16666666666669</v>
+        <v>379.85</v>
       </c>
       <c r="C13">
-        <v>5.0861111111111112</v>
+        <v>6.3308333333333335</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>14800</v>
+        <v>17237</v>
       </c>
       <c r="B14">
-        <v>246.66666666666666</v>
+        <v>287.28333333333336</v>
       </c>
       <c r="C14">
-        <v>4.1111111111111107</v>
+        <v>4.7880555555555553</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>15814</v>
+        <v>29302</v>
       </c>
       <c r="B15">
-        <v>263.56666666666666</v>
+        <v>488.36666666666667</v>
       </c>
       <c r="C15">
-        <v>4.3927777777777779</v>
+        <v>8.1394444444444449</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>18416</v>
+        <v>18526</v>
       </c>
       <c r="B16">
-        <v>306.93333333333334</v>
+        <v>308.76666666666665</v>
       </c>
       <c r="C16">
-        <v>5.1155555555555559</v>
+        <v>5.1461111111111109</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16894</v>
+        <v>19676</v>
       </c>
       <c r="B17">
-        <v>281.56666666666666</v>
+        <v>327.93333333333334</v>
       </c>
       <c r="C17">
-        <v>4.6927777777777777</v>
+        <v>5.4655555555555555</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>23383</v>
+        <v>17917</v>
       </c>
       <c r="B18">
-        <v>389.71666666666664</v>
+        <v>298.61666666666667</v>
       </c>
       <c r="C18">
-        <v>6.4952777777777779</v>
+        <v>4.9769444444444444</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>16284</v>
+        <v>22714</v>
       </c>
       <c r="B19">
-        <v>271.39999999999998</v>
+        <v>378.56666666666666</v>
       </c>
       <c r="C19">
-        <v>4.5233333333333334</v>
+        <v>6.3094444444444449</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>20268</v>
+        <v>19125</v>
       </c>
       <c r="B20">
-        <v>337.8</v>
+        <v>318.75</v>
       </c>
       <c r="C20">
-        <v>5.63</v>
+        <v>5.3125</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>18299</v>
+        <v>18403</v>
       </c>
       <c r="B21">
-        <v>304.98333333333335</v>
+        <v>306.71666666666664</v>
       </c>
       <c r="C21">
-        <v>5.0830555555555552</v>
+        <v>5.1119444444444442</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>15518</v>
+        <v>19929</v>
       </c>
       <c r="B22">
-        <v>258.63333333333333</v>
+        <v>332.15</v>
       </c>
       <c r="C22">
-        <v>4.3105555555555553</v>
+        <v>5.5358333333333336</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>18258</v>
+        <v>19198</v>
       </c>
       <c r="B23">
-        <v>304.3</v>
+        <v>319.96666666666664</v>
       </c>
       <c r="C23">
-        <v>5.0716666666666663</v>
+        <v>5.3327777777777774</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>14661</v>
+        <v>21127</v>
       </c>
       <c r="B24">
-        <v>244.35</v>
+        <v>352.11666666666667</v>
       </c>
       <c r="C24">
-        <v>4.0724999999999998</v>
+        <v>5.868611111111111</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>18435</v>
+        <v>21274</v>
       </c>
       <c r="B25">
-        <v>307.25</v>
+        <v>354.56666666666666</v>
       </c>
       <c r="C25">
-        <v>5.1208333333333336</v>
+        <v>5.9094444444444445</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>15699</v>
+        <v>18723</v>
       </c>
       <c r="B26">
-        <v>261.64999999999998</v>
+        <v>312.05</v>
       </c>
       <c r="C26">
-        <v>4.3608333333333329</v>
+        <v>5.2008333333333336</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>17490</v>
+        <v>21532</v>
       </c>
       <c r="B27">
-        <v>291.5</v>
+        <v>358.86666666666667</v>
       </c>
       <c r="C27">
-        <v>4.8583333333333334</v>
+        <v>5.9811111111111108</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>17610</v>
+        <v>19670</v>
       </c>
       <c r="B28">
-        <v>293.5</v>
+        <v>327.83333333333331</v>
       </c>
       <c r="C28">
-        <v>4.8916666666666666</v>
+        <v>5.4638888888888886</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>19275</v>
+        <v>21113</v>
       </c>
       <c r="B29">
-        <v>321.25</v>
+        <v>351.88333333333333</v>
       </c>
       <c r="C29">
-        <v>5.354166666666667</v>
+        <v>5.8647222222222224</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>15778</v>
+        <v>19465</v>
       </c>
       <c r="B30">
-        <v>262.96666666666664</v>
+        <v>324.41666666666669</v>
       </c>
       <c r="C30">
-        <v>4.3827777777777781</v>
+        <v>5.4069444444444441</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>16835</v>
+        <v>16728</v>
       </c>
       <c r="B31">
-        <v>280.58333333333331</v>
+        <v>278.8</v>
       </c>
       <c r="C31">
-        <v>4.6763888888888889</v>
+        <v>4.6466666666666665</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>17221</v>
+        <v>21089</v>
       </c>
       <c r="B32">
-        <v>287.01666666666665</v>
+        <v>351.48333333333335</v>
       </c>
       <c r="C32">
-        <v>4.783611111111111</v>
+        <v>5.8580555555555556</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>15998</v>
+        <v>23554</v>
       </c>
       <c r="B33">
-        <v>266.63333333333333</v>
+        <v>392.56666666666666</v>
       </c>
       <c r="C33">
-        <v>4.443888888888889</v>
+        <v>6.5427777777777774</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>15551</v>
+        <v>19923</v>
       </c>
       <c r="B34">
-        <v>259.18333333333334</v>
+        <v>332.05</v>
       </c>
       <c r="C34">
-        <v>4.3197222222222225</v>
+        <v>5.5341666666666667</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>16320</v>
+        <v>18413</v>
       </c>
       <c r="B35">
-        <v>272</v>
+        <v>306.88333333333333</v>
       </c>
       <c r="C35">
-        <v>4.5333333333333332</v>
+        <v>5.1147222222222224</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>17597</v>
+        <v>20004</v>
       </c>
       <c r="B36">
-        <v>293.28333333333336</v>
+        <v>333.4</v>
       </c>
       <c r="C36">
-        <v>4.8880555555555558</v>
+        <v>5.5566666666666666</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>16577</v>
+        <v>21440</v>
       </c>
       <c r="B37">
-        <v>276.28333333333336</v>
+        <v>357.33333333333331</v>
       </c>
       <c r="C37">
-        <v>4.6047222222222226</v>
+        <v>5.9555555555555557</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>17523</v>
+        <v>20410</v>
       </c>
       <c r="B38">
-        <v>292.05</v>
+        <v>340.16666666666669</v>
       </c>
       <c r="C38">
-        <v>4.8674999999999997</v>
+        <v>5.6694444444444443</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>16864</v>
+        <v>18257</v>
       </c>
       <c r="B39">
-        <v>281.06666666666666</v>
+        <v>304.28333333333336</v>
       </c>
       <c r="C39">
-        <v>4.6844444444444449</v>
+        <v>5.0713888888888885</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>17102</v>
+        <v>18387</v>
       </c>
       <c r="B40">
-        <v>285.03333333333336</v>
+        <v>306.45</v>
       </c>
       <c r="C40">
-        <v>4.7505555555555556</v>
+        <v>5.1074999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>17282</v>
+        <v>17769</v>
       </c>
       <c r="B41">
-        <v>288.03333333333336</v>
+        <v>296.14999999999998</v>
       </c>
       <c r="C41">
-        <v>4.8005555555555555</v>
+        <v>4.9358333333333331</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>16472</v>
+        <v>18215</v>
       </c>
       <c r="B42">
-        <v>274.53333333333336</v>
+        <v>303.58333333333331</v>
       </c>
       <c r="C42">
-        <v>4.5755555555555558</v>
+        <v>5.0597222222222218</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>14526</v>
+        <v>18278</v>
       </c>
       <c r="B43">
-        <v>242.1</v>
+        <v>304.63333333333333</v>
       </c>
       <c r="C43">
-        <v>4.0350000000000001</v>
+        <v>5.0772222222222219</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>16708</v>
+        <v>15891</v>
       </c>
       <c r="B44">
-        <v>278.46666666666664</v>
+        <v>264.85000000000002</v>
       </c>
       <c r="C44">
-        <v>4.641111111111111</v>
+        <v>4.4141666666666666</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>17392</v>
+        <v>18170</v>
       </c>
       <c r="B45">
-        <v>289.86666666666667</v>
+        <v>302.83333333333331</v>
       </c>
       <c r="C45">
-        <v>4.8311111111111114</v>
+        <v>5.0472222222222225</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>18781</v>
+        <v>16296</v>
       </c>
       <c r="B46">
-        <v>313.01666666666665</v>
+        <v>271.60000000000002</v>
       </c>
       <c r="C46">
-        <v>5.2169444444444446</v>
+        <v>4.5266666666666664</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>17353</v>
+        <v>18997</v>
       </c>
       <c r="B47">
-        <v>289.21666666666664</v>
+        <v>316.61666666666667</v>
       </c>
       <c r="C47">
-        <v>4.8202777777777781</v>
+        <v>5.2769444444444442</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>19775</v>
+        <v>18869</v>
       </c>
       <c r="B48">
-        <v>329.58333333333331</v>
+        <v>314.48333333333335</v>
       </c>
       <c r="C48">
-        <v>5.4930555555555554</v>
+        <v>5.2413888888888893</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>16158</v>
+        <v>22535</v>
       </c>
       <c r="B49">
-        <v>269.3</v>
+        <v>375.58333333333331</v>
       </c>
       <c r="C49">
-        <v>4.4883333333333333</v>
+        <v>6.259722222222222</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>15542</v>
+        <v>21755</v>
       </c>
       <c r="B50">
-        <v>259.03333333333336</v>
+        <v>362.58333333333331</v>
       </c>
       <c r="C50">
-        <v>4.3172222222222221</v>
+        <v>6.0430555555555552</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>19375</v>
+        <v>21313</v>
       </c>
       <c r="B51">
-        <v>322.91666666666669</v>
+        <v>355.21666666666664</v>
       </c>
       <c r="C51">
-        <v>5.3819444444444446</v>
+        <v>5.9202777777777778</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>16775</v>
+        <v>17382</v>
       </c>
       <c r="B52">
-        <v>279.58333333333331</v>
+        <v>289.7</v>
       </c>
       <c r="C52">
-        <v>4.6597222222222223</v>
+        <v>4.8283333333333331</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>14966</v>
+        <v>14158</v>
       </c>
       <c r="B53">
-        <v>249.43333333333334</v>
+        <v>235.96666666666667</v>
       </c>
       <c r="C53">
-        <v>4.1572222222222219</v>
+        <v>3.9327777777777779</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>18290</v>
+        <v>20453</v>
       </c>
       <c r="B54">
-        <v>304.83333333333331</v>
+        <v>340.88333333333333</v>
       </c>
       <c r="C54">
-        <v>5.0805555555555557</v>
+        <v>5.6813888888888888</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>16439</v>
+        <v>22570</v>
       </c>
       <c r="B55">
-        <v>273.98333333333335</v>
+        <v>376.16666666666669</v>
       </c>
       <c r="C55">
-        <v>4.5663888888888886</v>
+        <v>6.2694444444444448</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>16085</v>
+        <v>19834</v>
       </c>
       <c r="B56">
-        <v>268.08333333333331</v>
+        <v>330.56666666666666</v>
       </c>
       <c r="C56">
-        <v>4.4680555555555559</v>
+        <v>5.5094444444444441</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>15109</v>
+        <v>18073</v>
       </c>
       <c r="B57">
-        <v>251.81666666666666</v>
+        <v>301.21666666666664</v>
       </c>
       <c r="C57">
-        <v>4.1969444444444441</v>
+        <v>5.0202777777777774</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>16827</v>
+        <v>18467</v>
       </c>
       <c r="B58">
-        <v>280.45</v>
+        <v>307.78333333333336</v>
       </c>
       <c r="C58">
-        <v>4.6741666666666664</v>
+        <v>5.1297222222222221</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>17459</v>
+        <v>21549</v>
       </c>
       <c r="B59">
-        <v>290.98333333333335</v>
+        <v>359.15</v>
       </c>
       <c r="C59">
-        <v>4.8497222222222218</v>
+        <v>5.9858333333333329</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>16333</v>
+        <v>18859</v>
       </c>
       <c r="B60">
-        <v>272.21666666666664</v>
+        <v>314.31666666666666</v>
       </c>
       <c r="C60">
-        <v>4.536944444444444</v>
+        <v>5.2386111111111111</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>16709</v>
+        <v>20866</v>
       </c>
       <c r="B61">
-        <v>278.48333333333335</v>
+        <v>347.76666666666665</v>
       </c>
       <c r="C61">
-        <v>4.6413888888888888</v>
+        <v>5.7961111111111112</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>17258</v>
+        <v>15488</v>
       </c>
       <c r="B62">
-        <v>287.63333333333333</v>
+        <v>258.13333333333333</v>
       </c>
       <c r="C62">
-        <v>4.7938888888888886</v>
+        <v>4.3022222222222224</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>14761</v>
+        <v>18316</v>
       </c>
       <c r="B63">
-        <v>246.01666666666668</v>
+        <v>305.26666666666665</v>
       </c>
       <c r="C63">
-        <v>4.1002777777777775</v>
+        <v>5.0877777777777782</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>16775</v>
+        <v>16757</v>
       </c>
       <c r="B64">
-        <v>279.58333333333331</v>
+        <v>279.28333333333336</v>
       </c>
       <c r="C64">
-        <v>4.6597222222222223</v>
+        <v>4.6547222222222224</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>14020</v>
+        <v>19529</v>
       </c>
       <c r="B65">
-        <v>233.66666666666666</v>
+        <v>325.48333333333335</v>
       </c>
       <c r="C65">
-        <v>3.8944444444444444</v>
+        <v>5.424722222222222</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>16239</v>
+        <v>17115</v>
       </c>
       <c r="B66">
-        <v>270.64999999999998</v>
+        <v>285.25</v>
       </c>
       <c r="C66">
-        <v>4.5108333333333333</v>
+        <v>4.7541666666666664</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>14369</v>
+        <v>19810</v>
       </c>
       <c r="B67">
-        <v>239.48333333333332</v>
+        <v>330.16666666666669</v>
       </c>
       <c r="C67">
-        <v>3.9913888888888889</v>
+        <v>5.5027777777777782</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>17432</v>
+        <v>19675</v>
       </c>
       <c r="B68">
-        <v>290.53333333333336</v>
+        <v>327.91666666666669</v>
       </c>
       <c r="C68">
-        <v>4.8422222222222224</v>
+        <v>5.4652777777777777</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>17718</v>
+        <v>18232</v>
       </c>
       <c r="B69">
-        <v>295.3</v>
+        <v>303.86666666666667</v>
       </c>
       <c r="C69">
-        <v>4.9216666666666669</v>
+        <v>5.0644444444444447</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>15054</v>
+        <v>22855</v>
       </c>
       <c r="B70">
-        <v>250.9</v>
+        <v>380.91666666666669</v>
       </c>
       <c r="C70">
-        <v>4.1816666666666666</v>
+        <v>6.3486111111111114</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>14690</v>
+        <v>19714</v>
       </c>
       <c r="B71">
-        <v>244.83333333333334</v>
+        <v>328.56666666666666</v>
       </c>
       <c r="C71">
-        <v>4.0805555555555557</v>
+        <v>5.4761111111111109</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>18087</v>
+        <v>18637</v>
       </c>
       <c r="B72">
-        <v>301.45</v>
+        <v>310.61666666666667</v>
       </c>
       <c r="C72">
-        <v>5.0241666666666669</v>
+        <v>5.1769444444444446</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>15455</v>
+        <v>21934</v>
       </c>
       <c r="B73">
-        <v>257.58333333333331</v>
+        <v>365.56666666666666</v>
       </c>
       <c r="C73">
-        <v>4.2930555555555552</v>
+        <v>6.0927777777777781</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>17360</v>
+        <v>17978</v>
       </c>
       <c r="B74">
-        <v>289.33333333333331</v>
+        <v>299.63333333333333</v>
       </c>
       <c r="C74">
-        <v>4.822222222222222</v>
+        <v>4.9938888888888888</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>20873</v>
+        <v>18861</v>
       </c>
       <c r="B75">
-        <v>347.88333333333333</v>
+        <v>314.35000000000002</v>
       </c>
       <c r="C75">
-        <v>5.798055555555556</v>
+        <v>5.2391666666666667</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>17800</v>
+        <v>21769</v>
       </c>
       <c r="B76">
-        <v>296.66666666666669</v>
+        <v>362.81666666666666</v>
       </c>
       <c r="C76">
-        <v>4.9444444444444446</v>
+        <v>6.0469444444444447</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>17082</v>
+        <v>20414</v>
       </c>
       <c r="B77">
-        <v>284.7</v>
+        <v>340.23333333333335</v>
       </c>
       <c r="C77">
-        <v>4.7450000000000001</v>
+        <v>5.6705555555555556</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>17010</v>
+        <v>15837</v>
       </c>
       <c r="B78">
-        <v>283.5</v>
+        <v>263.95</v>
       </c>
       <c r="C78">
-        <v>4.7249999999999996</v>
+        <v>4.3991666666666669</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>16223</v>
+        <v>21813</v>
       </c>
       <c r="B79">
-        <v>270.38333333333333</v>
+        <v>363.55</v>
       </c>
       <c r="C79">
-        <v>4.506388888888889</v>
+        <v>6.059166666666667</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>20619</v>
+        <v>17380</v>
       </c>
       <c r="B80">
-        <v>343.65</v>
+        <v>289.66666666666669</v>
       </c>
       <c r="C80">
-        <v>5.7275</v>
+        <v>4.8277777777777775</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>17068</v>
+        <v>20122</v>
       </c>
       <c r="B81">
-        <v>284.46666666666664</v>
+        <v>335.36666666666667</v>
       </c>
       <c r="C81">
-        <v>4.7411111111111115</v>
+        <v>5.5894444444444442</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>18559</v>
+        <v>19410</v>
       </c>
       <c r="B82">
-        <v>309.31666666666666</v>
+        <v>323.5</v>
       </c>
       <c r="C82">
-        <v>5.1552777777777781</v>
+        <v>5.3916666666666666</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>16719</v>
+        <v>22338</v>
       </c>
       <c r="B83">
-        <v>278.64999999999998</v>
+        <v>372.3</v>
       </c>
       <c r="C83">
-        <v>4.644166666666667</v>
+        <v>6.2050000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>18323</v>
+        <v>18991</v>
       </c>
       <c r="B84">
-        <v>305.38333333333333</v>
+        <v>316.51666666666665</v>
       </c>
       <c r="C84">
-        <v>5.089722222222222</v>
+        <v>5.2752777777777782</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>16893</v>
+        <v>17290</v>
       </c>
       <c r="B85">
-        <v>281.55</v>
+        <v>288.16666666666669</v>
       </c>
       <c r="C85">
-        <v>4.6924999999999999</v>
+        <v>4.802777777777778</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>19397</v>
+        <v>20010</v>
       </c>
       <c r="B86">
-        <v>323.28333333333336</v>
+        <v>333.5</v>
       </c>
       <c r="C86">
-        <v>5.3880555555555558</v>
+        <v>5.5583333333333336</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>17573</v>
+        <v>21678</v>
       </c>
       <c r="B87">
-        <v>292.88333333333333</v>
+        <v>361.3</v>
       </c>
       <c r="C87">
-        <v>4.881388888888889</v>
+        <v>6.0216666666666665</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>16644</v>
+        <v>19946</v>
       </c>
       <c r="B88">
-        <v>277.39999999999998</v>
+        <v>332.43333333333334</v>
       </c>
       <c r="C88">
-        <v>4.6233333333333331</v>
+        <v>5.5405555555555557</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>16510</v>
+        <v>17375</v>
       </c>
       <c r="B89">
-        <v>275.16666666666669</v>
+        <v>289.58333333333331</v>
       </c>
       <c r="C89">
-        <v>4.5861111111111112</v>
+        <v>4.8263888888888893</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>17834</v>
+        <v>20391</v>
       </c>
       <c r="B90">
-        <v>297.23333333333335</v>
+        <v>339.85</v>
       </c>
       <c r="C90">
-        <v>4.9538888888888888</v>
+        <v>5.6641666666666666</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>16340</v>
+        <v>23005</v>
       </c>
       <c r="B91">
-        <v>272.33333333333331</v>
+        <v>383.41666666666669</v>
       </c>
       <c r="C91">
-        <v>4.5388888888888888</v>
+        <v>6.3902777777777775</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>17189</v>
+        <v>17818</v>
       </c>
       <c r="B92">
-        <v>286.48333333333335</v>
+        <v>296.96666666666664</v>
       </c>
       <c r="C92">
-        <v>4.7747222222222225</v>
+        <v>4.9494444444444445</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>15984</v>
+        <v>18917</v>
       </c>
       <c r="B93">
-        <v>266.39999999999998</v>
+        <v>315.28333333333336</v>
       </c>
       <c r="C93">
-        <v>4.4400000000000004</v>
+        <v>5.2547222222222221</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>17181</v>
+        <v>19667</v>
       </c>
       <c r="B94">
-        <v>286.35000000000002</v>
+        <v>327.78333333333336</v>
       </c>
       <c r="C94">
-        <v>4.7725</v>
+        <v>5.463055555555556</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>17910</v>
+        <v>18383</v>
       </c>
       <c r="B95">
-        <v>298.5</v>
+        <v>306.38333333333333</v>
       </c>
       <c r="C95">
-        <v>4.9749999999999996</v>
+        <v>5.1063888888888886</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>18310</v>
+        <v>19588</v>
       </c>
       <c r="B96">
-        <v>305.16666666666669</v>
+        <v>326.46666666666664</v>
       </c>
       <c r="C96">
-        <v>5.0861111111111112</v>
+        <v>5.4411111111111108</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>15632</v>
+        <v>18280</v>
       </c>
       <c r="B97">
-        <v>260.53333333333336</v>
+        <v>304.66666666666669</v>
       </c>
       <c r="C97">
-        <v>4.3422222222222224</v>
+        <v>5.0777777777777775</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>17093</v>
+        <v>25153</v>
       </c>
       <c r="B98">
-        <v>284.88333333333333</v>
+        <v>419.21666666666664</v>
       </c>
       <c r="C98">
-        <v>4.7480555555555553</v>
+        <v>6.9869444444444442</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>23264</v>
+        <v>20100</v>
       </c>
       <c r="B99">
-        <v>387.73333333333335</v>
+        <v>335</v>
       </c>
       <c r="C99">
-        <v>6.4622222222222225</v>
+        <v>5.583333333333333</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>15585</v>
+        <v>16033</v>
       </c>
       <c r="B100">
-        <v>259.75</v>
+        <v>267.21666666666664</v>
       </c>
       <c r="C100">
-        <v>4.3291666666666666</v>
+        <v>4.453611111111111</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>12418</v>
+        <v>19924</v>
       </c>
       <c r="B101">
-        <v>206.96666666666667</v>
+        <v>332.06666666666666</v>
       </c>
       <c r="C101">
-        <v>3.4494444444444445</v>
+        <v>5.5344444444444445</v>
       </c>
     </row>
   </sheetData>
@@ -2054,7 +2354,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B6A8E3-D8EB-4280-840A-346B01586132}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -2076,50 +2376,1120 @@
       <c r="A2">
         <v>32277</v>
       </c>
+      <c r="B2">
+        <f>A2/60</f>
+        <v>537.95000000000005</v>
+      </c>
+      <c r="C2">
+        <f>A2/3600</f>
+        <v>8.9658333333333342</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>59194</v>
       </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B11" si="0">A3/60</f>
+        <v>986.56666666666672</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C11" si="1">A3/3600</f>
+        <v>16.442777777777778</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>46634</v>
       </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>777.23333333333335</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="1"/>
+        <v>12.953888888888889</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>73295</v>
       </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>1221.5833333333333</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>20.359722222222221</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26560</v>
       </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>442.66666666666669</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>7.3777777777777782</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>24715</v>
       </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>411.91666666666669</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>6.865277777777778</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>56414</v>
       </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>940.23333333333335</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>15.670555555555556</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>72929</v>
       </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>1215.4833333333333</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>20.258055555555554</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25697</v>
       </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>428.28333333333336</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>7.1380555555555558</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>86400</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>1440</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>82886</v>
+      </c>
+      <c r="B12">
+        <v>1381.4333333333334</v>
+      </c>
+      <c r="C12">
+        <v>23.023888888888887</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>49086</v>
+      </c>
+      <c r="B13">
+        <v>818.1</v>
+      </c>
+      <c r="C13">
+        <v>13.635</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>32180</v>
+      </c>
+      <c r="B14">
+        <v>536.33333333333337</v>
+      </c>
+      <c r="C14">
+        <v>8.9388888888888882</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>62021</v>
+      </c>
+      <c r="B15">
+        <v>1033.6833333333334</v>
+      </c>
+      <c r="C15">
+        <v>17.228055555555557</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>20933</v>
+      </c>
+      <c r="B16">
+        <v>348.88333333333333</v>
+      </c>
+      <c r="C16">
+        <v>5.8147222222222226</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>43428</v>
+      </c>
+      <c r="B17">
+        <v>723.8</v>
+      </c>
+      <c r="C17">
+        <v>12.063333333333333</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>68500</v>
+      </c>
+      <c r="B18">
+        <v>1141.6666666666667</v>
+      </c>
+      <c r="C18">
+        <v>19.027777777777779</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18811</v>
+      </c>
+      <c r="B19">
+        <v>313.51666666666665</v>
+      </c>
+      <c r="C19">
+        <v>5.2252777777777775</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>21682</v>
+      </c>
+      <c r="B20">
+        <v>361.36666666666667</v>
+      </c>
+      <c r="C20">
+        <v>6.0227777777777778</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>21703</v>
+      </c>
+      <c r="B21">
+        <v>361.71666666666664</v>
+      </c>
+      <c r="C21">
+        <v>6.0286111111111111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>30874</v>
+      </c>
+      <c r="B22">
+        <v>514.56666666666672</v>
+      </c>
+      <c r="C22">
+        <v>8.5761111111111106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>56130</v>
+      </c>
+      <c r="B23">
+        <v>935.5</v>
+      </c>
+      <c r="C23">
+        <v>15.591666666666667</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>40566</v>
+      </c>
+      <c r="B24">
+        <v>676.1</v>
+      </c>
+      <c r="C24">
+        <v>11.268333333333333</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>86400</v>
+      </c>
+      <c r="B25">
+        <v>1440</v>
+      </c>
+      <c r="C25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>31588</v>
+      </c>
+      <c r="B26">
+        <v>526.4666666666667</v>
+      </c>
+      <c r="C26">
+        <v>8.7744444444444447</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>73878</v>
+      </c>
+      <c r="B27">
+        <v>1231.3</v>
+      </c>
+      <c r="C27">
+        <v>20.521666666666668</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>30991</v>
+      </c>
+      <c r="B28">
+        <v>516.51666666666665</v>
+      </c>
+      <c r="C28">
+        <v>8.6086111111111112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>86400</v>
+      </c>
+      <c r="B29">
+        <v>1440</v>
+      </c>
+      <c r="C29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>52802</v>
+      </c>
+      <c r="B30">
+        <v>880.0333333333333</v>
+      </c>
+      <c r="C30">
+        <v>14.667222222222222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>56560</v>
+      </c>
+      <c r="B31">
+        <v>942.66666666666663</v>
+      </c>
+      <c r="C31">
+        <v>15.71111111111111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>25229</v>
+      </c>
+      <c r="B32">
+        <v>420.48333333333335</v>
+      </c>
+      <c r="C32">
+        <v>7.0080555555555559</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>47442</v>
+      </c>
+      <c r="B33">
+        <v>790.7</v>
+      </c>
+      <c r="C33">
+        <v>13.178333333333333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>86400</v>
+      </c>
+      <c r="B34">
+        <v>1440</v>
+      </c>
+      <c r="C34">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>32426</v>
+      </c>
+      <c r="B35">
+        <v>540.43333333333328</v>
+      </c>
+      <c r="C35">
+        <v>9.0072222222222216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>34126</v>
+      </c>
+      <c r="B36">
+        <v>568.76666666666665</v>
+      </c>
+      <c r="C36">
+        <v>9.4794444444444448</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>71863</v>
+      </c>
+      <c r="B37">
+        <v>1197.7166666666667</v>
+      </c>
+      <c r="C37">
+        <v>19.961944444444445</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>86400</v>
+      </c>
+      <c r="B38">
+        <v>1440</v>
+      </c>
+      <c r="C38">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>80639</v>
+      </c>
+      <c r="B39">
+        <v>1343.9833333333333</v>
+      </c>
+      <c r="C39">
+        <v>22.399722222222223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>23770</v>
+      </c>
+      <c r="B40">
+        <v>396.16666666666669</v>
+      </c>
+      <c r="C40">
+        <v>6.6027777777777779</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>36796</v>
+      </c>
+      <c r="B41">
+        <v>613.26666666666665</v>
+      </c>
+      <c r="C41">
+        <v>10.221111111111112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>86400</v>
+      </c>
+      <c r="B42">
+        <v>1440</v>
+      </c>
+      <c r="C42">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42456</v>
+      </c>
+      <c r="B43">
+        <v>707.6</v>
+      </c>
+      <c r="C43">
+        <v>11.793333333333333</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>46865</v>
+      </c>
+      <c r="B44">
+        <v>781.08333333333337</v>
+      </c>
+      <c r="C44">
+        <v>13.018055555555556</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>39012</v>
+      </c>
+      <c r="B45">
+        <v>650.20000000000005</v>
+      </c>
+      <c r="C45">
+        <v>10.836666666666666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>57032</v>
+      </c>
+      <c r="B46">
+        <v>950.5333333333333</v>
+      </c>
+      <c r="C46">
+        <v>15.842222222222222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>27628</v>
+      </c>
+      <c r="B47">
+        <v>460.46666666666664</v>
+      </c>
+      <c r="C47">
+        <v>7.6744444444444442</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>24297</v>
+      </c>
+      <c r="B48">
+        <v>404.95</v>
+      </c>
+      <c r="C48">
+        <v>6.7491666666666665</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>60003</v>
+      </c>
+      <c r="B49">
+        <v>1000.05</v>
+      </c>
+      <c r="C49">
+        <v>16.6675</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>46577</v>
+      </c>
+      <c r="B50">
+        <v>776.2833333333333</v>
+      </c>
+      <c r="C50">
+        <v>12.938055555555556</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>86400</v>
+      </c>
+      <c r="B51">
+        <v>1440</v>
+      </c>
+      <c r="C51">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>25892</v>
+      </c>
+      <c r="B52">
+        <v>431.53333333333336</v>
+      </c>
+      <c r="C52">
+        <v>7.1922222222222221</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>31129</v>
+      </c>
+      <c r="B53">
+        <v>518.81666666666672</v>
+      </c>
+      <c r="C53">
+        <v>8.6469444444444452</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>20795</v>
+      </c>
+      <c r="B54">
+        <v>346.58333333333331</v>
+      </c>
+      <c r="C54">
+        <v>5.7763888888888886</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>52130</v>
+      </c>
+      <c r="B55">
+        <v>868.83333333333337</v>
+      </c>
+      <c r="C55">
+        <v>14.480555555555556</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>30922</v>
+      </c>
+      <c r="B56">
+        <v>515.36666666666667</v>
+      </c>
+      <c r="C56">
+        <v>8.5894444444444442</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>19406</v>
+      </c>
+      <c r="B57">
+        <v>323.43333333333334</v>
+      </c>
+      <c r="C57">
+        <v>5.3905555555555553</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>50145</v>
+      </c>
+      <c r="B58">
+        <v>835.75</v>
+      </c>
+      <c r="C58">
+        <v>13.929166666666667</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>32009</v>
+      </c>
+      <c r="B59">
+        <v>533.48333333333335</v>
+      </c>
+      <c r="C59">
+        <v>8.8913888888888888</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>86400</v>
+      </c>
+      <c r="B60">
+        <v>1440</v>
+      </c>
+      <c r="C60">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>16011</v>
+      </c>
+      <c r="B61">
+        <v>266.85000000000002</v>
+      </c>
+      <c r="C61">
+        <v>4.4474999999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>38381</v>
+      </c>
+      <c r="B62">
+        <v>639.68333333333328</v>
+      </c>
+      <c r="C62">
+        <v>10.661388888888888</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>19573</v>
+      </c>
+      <c r="B63">
+        <v>326.21666666666664</v>
+      </c>
+      <c r="C63">
+        <v>5.4369444444444444</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>60334</v>
+      </c>
+      <c r="B64">
+        <v>1005.5666666666667</v>
+      </c>
+      <c r="C64">
+        <v>16.759444444444444</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>21026</v>
+      </c>
+      <c r="B65">
+        <v>350.43333333333334</v>
+      </c>
+      <c r="C65">
+        <v>5.8405555555555555</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>63215</v>
+      </c>
+      <c r="B66">
+        <v>1053.5833333333333</v>
+      </c>
+      <c r="C66">
+        <v>17.559722222222224</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>61757</v>
+      </c>
+      <c r="B67">
+        <v>1029.2833333333333</v>
+      </c>
+      <c r="C67">
+        <v>17.154722222222222</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>31685</v>
+      </c>
+      <c r="B68">
+        <v>528.08333333333337</v>
+      </c>
+      <c r="C68">
+        <v>8.8013888888888889</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>86400</v>
+      </c>
+      <c r="B69">
+        <v>1440</v>
+      </c>
+      <c r="C69">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>53183</v>
+      </c>
+      <c r="B70">
+        <v>886.38333333333333</v>
+      </c>
+      <c r="C70">
+        <v>14.773055555555555</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>22151</v>
+      </c>
+      <c r="B71">
+        <v>369.18333333333334</v>
+      </c>
+      <c r="C71">
+        <v>6.1530555555555555</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>52395</v>
+      </c>
+      <c r="B72">
+        <v>873.25</v>
+      </c>
+      <c r="C72">
+        <v>14.554166666666667</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>37095</v>
+      </c>
+      <c r="B73">
+        <v>618.25</v>
+      </c>
+      <c r="C73">
+        <v>10.304166666666667</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>74801</v>
+      </c>
+      <c r="B74">
+        <v>1246.6833333333334</v>
+      </c>
+      <c r="C74">
+        <v>20.778055555555557</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>37757</v>
+      </c>
+      <c r="B75">
+        <v>629.2833333333333</v>
+      </c>
+      <c r="C75">
+        <v>10.488055555555556</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>50038</v>
+      </c>
+      <c r="B76">
+        <v>833.9666666666667</v>
+      </c>
+      <c r="C76">
+        <v>13.899444444444445</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>23750</v>
+      </c>
+      <c r="B77">
+        <v>395.83333333333331</v>
+      </c>
+      <c r="C77">
+        <v>6.5972222222222223</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>86400</v>
+      </c>
+      <c r="B78">
+        <v>1440</v>
+      </c>
+      <c r="C78">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>86400</v>
+      </c>
+      <c r="B79">
+        <v>1440</v>
+      </c>
+      <c r="C79">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>36391</v>
+      </c>
+      <c r="B80">
+        <v>606.51666666666665</v>
+      </c>
+      <c r="C80">
+        <v>10.108611111111111</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>64251</v>
+      </c>
+      <c r="B81">
+        <v>1070.8499999999999</v>
+      </c>
+      <c r="C81">
+        <v>17.8475</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>86400</v>
+      </c>
+      <c r="B82">
+        <v>1440</v>
+      </c>
+      <c r="C82">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>53476</v>
+      </c>
+      <c r="B83">
+        <v>891.26666666666665</v>
+      </c>
+      <c r="C83">
+        <v>14.854444444444445</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>25874</v>
+      </c>
+      <c r="B84">
+        <v>431.23333333333335</v>
+      </c>
+      <c r="C84">
+        <v>7.1872222222222222</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>78489</v>
+      </c>
+      <c r="B85">
+        <v>1308.1500000000001</v>
+      </c>
+      <c r="C85">
+        <v>21.802499999999998</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>73979</v>
+      </c>
+      <c r="B86">
+        <v>1232.9833333333333</v>
+      </c>
+      <c r="C86">
+        <v>20.549722222222222</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86400</v>
+      </c>
+      <c r="B87">
+        <v>1440</v>
+      </c>
+      <c r="C87">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>57069</v>
+      </c>
+      <c r="B88">
+        <v>951.15</v>
+      </c>
+      <c r="C88">
+        <v>15.852499999999999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>29866</v>
+      </c>
+      <c r="B89">
+        <v>497.76666666666665</v>
+      </c>
+      <c r="C89">
+        <v>8.2961111111111112</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>42467</v>
+      </c>
+      <c r="B90">
+        <v>707.7833333333333</v>
+      </c>
+      <c r="C90">
+        <v>11.796388888888888</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>82097</v>
+      </c>
+      <c r="B91">
+        <v>1368.2833333333333</v>
+      </c>
+      <c r="C91">
+        <v>22.804722222222221</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>27486</v>
+      </c>
+      <c r="B92">
+        <v>458.1</v>
+      </c>
+      <c r="C92">
+        <v>7.6349999999999998</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>53809</v>
+      </c>
+      <c r="B93">
+        <v>896.81666666666672</v>
+      </c>
+      <c r="C93">
+        <v>14.946944444444444</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>78106</v>
+      </c>
+      <c r="B94">
+        <v>1301.7666666666667</v>
+      </c>
+      <c r="C94">
+        <v>21.696111111111112</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>20883</v>
+      </c>
+      <c r="B95">
+        <v>348.05</v>
+      </c>
+      <c r="C95">
+        <v>5.8008333333333333</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>26449</v>
+      </c>
+      <c r="B96">
+        <v>440.81666666666666</v>
+      </c>
+      <c r="C96">
+        <v>7.3469444444444445</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>17196</v>
+      </c>
+      <c r="B97">
+        <v>286.60000000000002</v>
+      </c>
+      <c r="C97">
+        <v>4.7766666666666664</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>46726</v>
+      </c>
+      <c r="B98">
+        <v>778.76666666666665</v>
+      </c>
+      <c r="C98">
+        <v>12.979444444444445</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>43138</v>
+      </c>
+      <c r="B99">
+        <v>718.9666666666667</v>
+      </c>
+      <c r="C99">
+        <v>11.982777777777779</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>26322</v>
+      </c>
+      <c r="B100">
+        <v>438.7</v>
+      </c>
+      <c r="C100">
+        <v>7.3116666666666665</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>27136</v>
+      </c>
+      <c r="B101">
+        <v>452.26666666666665</v>
+      </c>
+      <c r="C101">
+        <v>7.5377777777777775</v>
       </c>
     </row>
   </sheetData>
